--- a/products/Schedule Health Checklist.xlsx
+++ b/products/Schedule Health Checklist.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Checklist'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +54,12 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0033415C"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -76,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -98,11 +106,16 @@
         <color rgb="00DDE3EA"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00DDE3EA"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -133,6 +146,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -495,10 +510,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -809,16 +825,30 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>CPM Toolkit  |  Schedule Health Checklist  |  v1.0</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D5:D18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Flag,N/A"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>